--- a/artfynd/A 12524-2024 artfynd.xlsx
+++ b/artfynd/A 12524-2024 artfynd.xlsx
@@ -6089,10 +6089,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120809209</v>
+        <v>120809214</v>
       </c>
       <c r="B54" t="n">
-        <v>98071</v>
+        <v>78598</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6101,25 +6101,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6129,10 +6129,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>879254</v>
+        <v>879418</v>
       </c>
       <c r="R54" t="n">
-        <v>7405656</v>
+        <v>7405537</v>
       </c>
       <c r="S54" t="n">
         <v>1</v>
@@ -6191,10 +6191,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120809214</v>
+        <v>120809200</v>
       </c>
       <c r="B55" t="n">
-        <v>78598</v>
+        <v>79708</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6203,25 +6203,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6231,10 +6231,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>879418</v>
+        <v>879437</v>
       </c>
       <c r="R55" t="n">
-        <v>7405537</v>
+        <v>7405529</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -6293,10 +6293,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120809200</v>
+        <v>120809209</v>
       </c>
       <c r="B56" t="n">
-        <v>79708</v>
+        <v>98071</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6305,25 +6305,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6333,10 +6333,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>879437</v>
+        <v>879254</v>
       </c>
       <c r="R56" t="n">
-        <v>7405529</v>
+        <v>7405656</v>
       </c>
       <c r="S56" t="n">
         <v>1</v>

--- a/artfynd/A 12524-2024 artfynd.xlsx
+++ b/artfynd/A 12524-2024 artfynd.xlsx
@@ -5579,10 +5579,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120804884</v>
+        <v>120809195</v>
       </c>
       <c r="B49" t="n">
-        <v>79708</v>
+        <v>57351</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5591,25 +5591,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5619,10 +5619,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>879442</v>
+        <v>879353</v>
       </c>
       <c r="R49" t="n">
-        <v>7405533</v>
+        <v>7405615</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -5657,6 +5657,11 @@
           <t>2024-11-01</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5669,22 +5674,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120804886</v>
+        <v>120809214</v>
       </c>
       <c r="B50" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5693,25 +5698,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5721,10 +5726,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>879271</v>
+        <v>879418</v>
       </c>
       <c r="R50" t="n">
-        <v>7405707</v>
+        <v>7405537</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -5771,22 +5776,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120804890</v>
+        <v>120809201</v>
       </c>
       <c r="B51" t="n">
-        <v>78598</v>
+        <v>79711</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5795,25 +5800,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5823,10 +5828,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>879171</v>
+        <v>879439</v>
       </c>
       <c r="R51" t="n">
-        <v>7405678</v>
+        <v>7405528</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -5873,12 +5878,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5888,7 +5893,7 @@
         <v>120804882</v>
       </c>
       <c r="B52" t="n">
-        <v>79708</v>
+        <v>79711</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5987,10 +5992,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120804888</v>
+        <v>120809209</v>
       </c>
       <c r="B53" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5999,25 +6004,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6027,10 +6032,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>879358</v>
+        <v>879254</v>
       </c>
       <c r="R53" t="n">
-        <v>7405614</v>
+        <v>7405656</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -6077,22 +6082,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120809214</v>
+        <v>120804890</v>
       </c>
       <c r="B54" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6129,10 +6134,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>879418</v>
+        <v>879171</v>
       </c>
       <c r="R54" t="n">
-        <v>7405537</v>
+        <v>7405678</v>
       </c>
       <c r="S54" t="n">
         <v>1</v>
@@ -6179,22 +6184,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120809200</v>
+        <v>120809199</v>
       </c>
       <c r="B55" t="n">
-        <v>79708</v>
+        <v>79711</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6231,10 +6236,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>879437</v>
+        <v>879418</v>
       </c>
       <c r="R55" t="n">
-        <v>7405529</v>
+        <v>7405537</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -6293,10 +6298,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120809209</v>
+        <v>120804887</v>
       </c>
       <c r="B56" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6305,25 +6310,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6333,10 +6338,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>879254</v>
+        <v>879430</v>
       </c>
       <c r="R56" t="n">
-        <v>7405656</v>
+        <v>7405704</v>
       </c>
       <c r="S56" t="n">
         <v>1</v>
@@ -6383,22 +6388,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120809207</v>
+        <v>120809203</v>
       </c>
       <c r="B57" t="n">
-        <v>79707</v>
+        <v>57367</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6407,25 +6412,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6435,10 +6440,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>879288</v>
+        <v>879251</v>
       </c>
       <c r="R57" t="n">
-        <v>7405647</v>
+        <v>7405485</v>
       </c>
       <c r="S57" t="n">
         <v>1</v>
@@ -6471,6 +6476,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6497,10 +6507,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120809195</v>
+        <v>120804881</v>
       </c>
       <c r="B58" t="n">
-        <v>57348</v>
+        <v>79711</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6509,25 +6519,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6537,10 +6547,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>879353</v>
+        <v>879463</v>
       </c>
       <c r="R58" t="n">
-        <v>7405615</v>
+        <v>7405765</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
@@ -6575,11 +6585,6 @@
           <t>2024-11-01</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6592,22 +6597,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120804887</v>
+        <v>120804886</v>
       </c>
       <c r="B59" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6616,25 +6621,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6644,10 +6649,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>879430</v>
+        <v>879271</v>
       </c>
       <c r="R59" t="n">
-        <v>7405704</v>
+        <v>7405707</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -6706,10 +6711,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120809197</v>
+        <v>120809213</v>
       </c>
       <c r="B60" t="n">
-        <v>79708</v>
+        <v>78601</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6718,25 +6723,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6746,10 +6751,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>879361</v>
+        <v>879130</v>
       </c>
       <c r="R60" t="n">
-        <v>7405521</v>
+        <v>7405509</v>
       </c>
       <c r="S60" t="n">
         <v>1</v>
@@ -6808,10 +6813,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120809205</v>
+        <v>120804884</v>
       </c>
       <c r="B61" t="n">
-        <v>79583</v>
+        <v>79711</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6824,21 +6829,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6848,10 +6853,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>879491</v>
+        <v>879442</v>
       </c>
       <c r="R61" t="n">
-        <v>7405666</v>
+        <v>7405533</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -6898,22 +6903,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120809212</v>
+        <v>120809210</v>
       </c>
       <c r="B62" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6950,10 +6955,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>879294</v>
+        <v>879501</v>
       </c>
       <c r="R62" t="n">
-        <v>7405620</v>
+        <v>7405781</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7012,10 +7017,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120809210</v>
+        <v>120809202</v>
       </c>
       <c r="B63" t="n">
-        <v>78598</v>
+        <v>90708</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7024,25 +7029,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7052,10 +7057,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>879501</v>
+        <v>879283</v>
       </c>
       <c r="R63" t="n">
-        <v>7405781</v>
+        <v>7405644</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -7114,10 +7119,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120804889</v>
+        <v>120804891</v>
       </c>
       <c r="B64" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7154,10 +7159,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>879223</v>
+        <v>879125</v>
       </c>
       <c r="R64" t="n">
-        <v>7405676</v>
+        <v>7405649</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -7209,17 +7214,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120809204</v>
+        <v>120804880</v>
       </c>
       <c r="B65" t="n">
-        <v>57364</v>
+        <v>79711</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7228,25 +7233,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7256,10 +7261,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>879448</v>
+        <v>879502</v>
       </c>
       <c r="R65" t="n">
-        <v>7405509</v>
+        <v>7405789</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -7294,11 +7299,6 @@
           <t>2024-11-01</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Avbarkad tall</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7311,22 +7311,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120804880</v>
+        <v>120804885</v>
       </c>
       <c r="B66" t="n">
-        <v>79708</v>
+        <v>98081</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7335,25 +7335,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7363,10 +7363,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>879502</v>
+        <v>879282</v>
       </c>
       <c r="R66" t="n">
-        <v>7405789</v>
+        <v>7405713</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -7425,10 +7425,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120809202</v>
+        <v>120809204</v>
       </c>
       <c r="B67" t="n">
-        <v>90698</v>
+        <v>57367</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7437,25 +7437,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7465,10 +7465,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>879283</v>
+        <v>879448</v>
       </c>
       <c r="R67" t="n">
-        <v>7405644</v>
+        <v>7405509</v>
       </c>
       <c r="S67" t="n">
         <v>1</v>
@@ -7501,6 +7501,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7527,10 +7532,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120809201</v>
+        <v>120809207</v>
       </c>
       <c r="B68" t="n">
-        <v>79708</v>
+        <v>79710</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7543,21 +7548,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7567,10 +7572,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>879439</v>
+        <v>879288</v>
       </c>
       <c r="R68" t="n">
-        <v>7405528</v>
+        <v>7405647</v>
       </c>
       <c r="S68" t="n">
         <v>1</v>
@@ -7629,10 +7634,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120804885</v>
+        <v>120809205</v>
       </c>
       <c r="B69" t="n">
-        <v>98071</v>
+        <v>79586</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7641,25 +7646,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7669,10 +7674,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>879282</v>
+        <v>879491</v>
       </c>
       <c r="R69" t="n">
-        <v>7405713</v>
+        <v>7405666</v>
       </c>
       <c r="S69" t="n">
         <v>1</v>
@@ -7719,22 +7724,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120809213</v>
+        <v>120809212</v>
       </c>
       <c r="B70" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7771,10 +7776,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>879130</v>
+        <v>879294</v>
       </c>
       <c r="R70" t="n">
-        <v>7405509</v>
+        <v>7405620</v>
       </c>
       <c r="S70" t="n">
         <v>1</v>
@@ -7833,10 +7838,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120809199</v>
+        <v>120809211</v>
       </c>
       <c r="B71" t="n">
-        <v>79708</v>
+        <v>78601</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7845,25 +7850,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7873,10 +7878,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>879418</v>
+        <v>879347</v>
       </c>
       <c r="R71" t="n">
-        <v>7405537</v>
+        <v>7405612</v>
       </c>
       <c r="S71" t="n">
         <v>1</v>
@@ -7935,10 +7940,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120809196</v>
+        <v>120809200</v>
       </c>
       <c r="B72" t="n">
-        <v>79708</v>
+        <v>79711</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7975,10 +7980,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>879502</v>
+        <v>879437</v>
       </c>
       <c r="R72" t="n">
-        <v>7405779</v>
+        <v>7405529</v>
       </c>
       <c r="S72" t="n">
         <v>1</v>
@@ -8037,10 +8042,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120804881</v>
+        <v>120804889</v>
       </c>
       <c r="B73" t="n">
-        <v>79708</v>
+        <v>78601</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8049,25 +8054,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8077,10 +8082,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>879463</v>
+        <v>879223</v>
       </c>
       <c r="R73" t="n">
-        <v>7405765</v>
+        <v>7405676</v>
       </c>
       <c r="S73" t="n">
         <v>1</v>
@@ -8132,17 +8137,17 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120809194</v>
+        <v>120804888</v>
       </c>
       <c r="B74" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8155,21 +8160,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8179,10 +8184,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>879427</v>
+        <v>879358</v>
       </c>
       <c r="R74" t="n">
-        <v>7405493</v>
+        <v>7405614</v>
       </c>
       <c r="S74" t="n">
         <v>1</v>
@@ -8217,11 +8222,6 @@
           <t>2024-11-01</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -8234,22 +8234,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120809211</v>
+        <v>120809194</v>
       </c>
       <c r="B75" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8262,21 +8262,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8286,10 +8286,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>879347</v>
+        <v>879427</v>
       </c>
       <c r="R75" t="n">
-        <v>7405612</v>
+        <v>7405493</v>
       </c>
       <c r="S75" t="n">
         <v>1</v>
@@ -8322,6 +8322,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8348,10 +8353,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120809206</v>
+        <v>120809197</v>
       </c>
       <c r="B76" t="n">
-        <v>79583</v>
+        <v>79711</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8364,21 +8369,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8388,10 +8393,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>879334</v>
+        <v>879361</v>
       </c>
       <c r="R76" t="n">
-        <v>7405588</v>
+        <v>7405521</v>
       </c>
       <c r="S76" t="n">
         <v>1</v>
@@ -8450,10 +8455,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120809215</v>
+        <v>120809206</v>
       </c>
       <c r="B77" t="n">
-        <v>79714</v>
+        <v>79586</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8466,21 +8471,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8490,10 +8495,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>879459</v>
+        <v>879334</v>
       </c>
       <c r="R77" t="n">
-        <v>7405757</v>
+        <v>7405588</v>
       </c>
       <c r="S77" t="n">
         <v>1</v>
@@ -8552,10 +8557,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120804891</v>
+        <v>120809215</v>
       </c>
       <c r="B78" t="n">
-        <v>78598</v>
+        <v>79717</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8564,20 +8569,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -8592,10 +8597,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>879125</v>
+        <v>879459</v>
       </c>
       <c r="R78" t="n">
-        <v>7405649</v>
+        <v>7405757</v>
       </c>
       <c r="S78" t="n">
         <v>1</v>
@@ -8642,22 +8647,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120809203</v>
+        <v>120809196</v>
       </c>
       <c r="B79" t="n">
-        <v>57364</v>
+        <v>79711</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8666,25 +8671,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8694,10 +8699,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>879251</v>
+        <v>879502</v>
       </c>
       <c r="R79" t="n">
-        <v>7405485</v>
+        <v>7405779</v>
       </c>
       <c r="S79" t="n">
         <v>1</v>
@@ -8730,11 +8735,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-11-01</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Avbarkad tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
